--- a/artfynd/A 38400-2023 artfynd.xlsx
+++ b/artfynd/A 38400-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38400-2023 artfynd.xlsx
+++ b/artfynd/A 38400-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>98345633</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557996.2624043832</v>
+        <v>557996</v>
       </c>
       <c r="R2" t="n">
-        <v>6835099.242386522</v>
+        <v>6835099</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +760,9 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,12 +788,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 38400-2023 artfynd.xlsx
+++ b/artfynd/A 38400-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>98345633</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,12 +788,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 38400-2023 artfynd.xlsx
+++ b/artfynd/A 38400-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>98345633</v>
       </c>
       <c r="B2" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 38400-2023 artfynd.xlsx
+++ b/artfynd/A 38400-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>98345633</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 38400-2023 artfynd.xlsx
+++ b/artfynd/A 38400-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>98345633</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 38400-2023 artfynd.xlsx
+++ b/artfynd/A 38400-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>98345633</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 38400-2023 artfynd.xlsx
+++ b/artfynd/A 38400-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>98345633</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
